--- a/data/deployments.xlsx
+++ b/data/deployments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\local_mydev\tropical_forages_ai_guidelines\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3060B40-3AD5-433A-B130-2BB1FE343E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBEAC4B2-18E2-473B-8A62-CA7754C86A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2CFBF07F-C8C2-4B4A-BFF2-44C9E7F2338D}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2CFBF07F-C8C2-4B4A-BFF2-44C9E7F2338D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>CGSPACE</t>
   </si>
@@ -60,6 +60,72 @@
   </si>
   <si>
     <t>https://cgspace.cgiar.org/items/398116cc-deba-432c-b438-74f3bb04c784</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/afruizh/root_analysis </t>
+  </si>
+  <si>
+    <t>RootingAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/afruizh/forages_rois </t>
+  </si>
+  <si>
+    <t>ForagesROIs</t>
+  </si>
+  <si>
+    <t>Root segmentation for underground root scanners</t>
+  </si>
+  <si>
+    <t>Forage grass detection in crop fields</t>
+  </si>
+  <si>
+    <t>Raceme detection and counting</t>
+  </si>
+  <si>
+    <t>BrRacemecounter</t>
+  </si>
+  <si>
+    <t>GrassDamageAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damage classification and quantification </t>
+  </si>
+  <si>
+    <t>https://github.com/afruizh/damage_assessment_pipeline</t>
+  </si>
+  <si>
+    <t>https://github.com/darwin-arrechea-castillo/Mask_RCNN-Raceme_Instance_Segmentation</t>
+  </si>
+  <si>
+    <t>Forages Chatbot</t>
+  </si>
+  <si>
+    <t>RAG Agent tropical forages research assistant chatbot</t>
+  </si>
+  <si>
+    <t>https://github.com/afruizh/forages_chatbot_streamlit</t>
+  </si>
+  <si>
+    <t>treeeyed.jpg</t>
+  </si>
+  <si>
+    <t>rootingai.jpg</t>
+  </si>
+  <si>
+    <t>foragesrois.jpg</t>
+  </si>
+  <si>
+    <t>brracemecounter.jpg</t>
+  </si>
+  <si>
+    <t>grassdamageai.jpg</t>
+  </si>
+  <si>
+    <t>chatbot.jpg</t>
   </si>
 </sst>
 </file>
@@ -104,9 +170,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -442,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A44C2EA-5790-49C3-B629-C4C555CFBE06}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -450,7 +519,7 @@
     <col min="3" max="3" width="75.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -463,8 +532,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -476,13 +548,92 @@
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{5830E766-3D3E-4EDC-B7FF-3883D60D0016}"/>
     <hyperlink ref="A2" r:id="rId2" xr:uid="{95C5DF26-577B-4B58-9E37-F80F01B58D8F}"/>
+    <hyperlink ref="D3" r:id="rId3" display="https://github.com/afruizh/root_analysis" xr:uid="{81F823E2-E5CE-4168-9332-4C9BF01DDA76}"/>
+    <hyperlink ref="D4" r:id="rId4" xr:uid="{36974B40-78AF-4A52-BAC7-8E49C4E35B7A}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{635B36EB-728E-4FDA-B4A7-59BDF1F46646}"/>
+    <hyperlink ref="D5" r:id="rId6" xr:uid="{44CDB049-C794-43B0-83AC-1D59ED473F79}"/>
+    <hyperlink ref="D7" r:id="rId7" xr:uid="{7141F923-0551-404A-8E55-45B44A639FB8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>